--- a/tests/retriever_test.xlsx
+++ b/tests/retriever_test.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
   <si>
     <t>f_A</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>d3</t>
+  </si>
+  <si>
+    <t>a2</t>
+  </si>
+  <si>
+    <t>c2</t>
   </si>
 </sst>
 </file>
@@ -387,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -469,32 +475,49 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D7" t="s">
-        <v>15</v>
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>18</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
       <c r="D8" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="D9" t="s">
         <v>16</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E9" t="s">
         <v>9</v>
       </c>
-      <c r="F8">
+      <c r="F9">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E9" t="s">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E10" t="s">
         <v>10</v>
       </c>
-      <c r="F9" t="s">
+      <c r="F10" t="s">
         <v>11</v>
       </c>
     </row>

--- a/tests/retriever_test.xlsx
+++ b/tests/retriever_test.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
   <si>
     <t>f_A</t>
   </si>
@@ -76,6 +76,12 @@
   </si>
   <si>
     <t>c2</t>
+  </si>
+  <si>
+    <t>six</t>
+  </si>
+  <si>
+    <t>retriever_test2.csv</t>
   </si>
 </sst>
 </file>
@@ -393,7 +399,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -521,6 +527,14 @@
         <v>11</v>
       </c>
     </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="E11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/tests/retriever_test.xlsx
+++ b/tests/retriever_test.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="34">
   <si>
     <t>f_A</t>
   </si>
@@ -82,14 +82,61 @@
   </si>
   <si>
     <t>retriever_test2.csv</t>
+  </si>
+  <si>
+    <t>seven</t>
+  </si>
+  <si>
+    <t>a3</t>
+  </si>
+  <si>
+    <t>a4</t>
+  </si>
+  <si>
+    <t>ag1</t>
+  </si>
+  <si>
+    <t>ag2</t>
+  </si>
+  <si>
+    <t>f_AG:A</t>
+  </si>
+  <si>
+    <t>eight</t>
+  </si>
+  <si>
+    <t>f_GG:G</t>
+  </si>
+  <si>
+    <t>gg1</t>
+  </si>
+  <si>
+    <t>nine</t>
+  </si>
+  <si>
+    <t>gg2</t>
+  </si>
+  <si>
+    <t>f_BG:B</t>
+  </si>
+  <si>
+    <t>bg1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -117,8 +164,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -399,140 +447,260 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E2" t="s">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H2" t="s">
         <v>6</v>
       </c>
-      <c r="F2">
+      <c r="I2">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
-      <c r="E3" t="s">
+      <c r="H3" t="s">
         <v>6</v>
       </c>
-      <c r="F3">
+      <c r="I3">
         <v>1.2</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>6</v>
       </c>
-      <c r="F4">
+      <c r="I4">
         <v>1.3</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>13</v>
       </c>
-      <c r="C5" t="s">
+      <c r="E5" t="s">
         <v>14</v>
       </c>
-      <c r="E5" t="s">
+      <c r="H5" t="s">
         <v>6</v>
       </c>
-      <c r="F5">
+      <c r="I5">
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E6" t="s">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H6" t="s">
         <v>7</v>
       </c>
-      <c r="F6">
+      <c r="I6">
         <v>2</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>17</v>
       </c>
-      <c r="C7" t="s">
+      <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="E7" t="s">
+      <c r="H7" t="s">
         <v>8</v>
       </c>
-      <c r="F7">
+      <c r="I7">
         <v>3.1</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>17</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="H8" t="s">
         <v>8</v>
       </c>
-      <c r="F8">
+      <c r="I8">
         <v>3.2</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="D9" t="s">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F9" t="s">
         <v>16</v>
       </c>
-      <c r="E9" t="s">
+      <c r="H9" t="s">
         <v>9</v>
       </c>
-      <c r="F9">
+      <c r="I9">
         <v>4</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E10" t="s">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H10" t="s">
         <v>10</v>
       </c>
-      <c r="F10" t="s">
+      <c r="I10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="E11" t="s">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="H11" t="s">
         <v>19</v>
       </c>
-      <c r="F11" t="s">
+      <c r="I11" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I12">
+        <v>7.1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I13">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>22</v>
+      </c>
+      <c r="H14" t="s">
+        <v>21</v>
+      </c>
+      <c r="I14">
+        <v>7.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" t="s">
+        <v>21</v>
+      </c>
+      <c r="I15">
+        <v>7.4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+      <c r="H16" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="H17" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17">
+        <v>8.1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" t="s">
+        <v>29</v>
+      </c>
+      <c r="H18" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18">
+        <v>8.1999999999999993</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G19" t="s">
+        <v>29</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19">
+        <v>9.1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D20" t="s">
+        <v>33</v>
+      </c>
+      <c r="G20" t="s">
+        <v>31</v>
+      </c>
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20">
+        <v>9.1999999999999993</v>
       </c>
     </row>
   </sheetData>
